--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>06/26 08:48:20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>36144.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>460000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55192.2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>36144.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>55192.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/26 14:18:46</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55192</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>460000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>55192.2</t>
+          <t>460000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55192.2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>55192</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>55192.2</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>460000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>55192.2</t>
+          <t>560000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>55192</t>
+          <t>67096.96</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>55192</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11904.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>560000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>67096.96</t>
+          <t>560000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>55192</t>
+          <t>67096.96</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>67096</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>11904.96</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>560000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>67096.96</t>
+          <t>860000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>67096</t>
+          <t>103241.54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>67096</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.96</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>36145.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>860000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>103241.54</t>
+          <t>860000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>67096</t>
+          <t>103241.54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>103240</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>36145.54</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>860000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>103241.54</t>
+          <t>1860000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>103240</t>
+          <t>222289.16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>103240</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1.54</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>119049.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,83 +424,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1860000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>222289.16</t>
+          <t>1860000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>103240</t>
+          <t>222289.16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>222287</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>119049.16</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,83 +466,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1860000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>222289.16</t>
+          <t>2060000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>222287</t>
+          <t>246385.54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>222287</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2.16</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>24098.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,83 +493,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2060000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>246385.54</t>
+          <t>2060000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>222287</t>
+          <t>246385.54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>246383</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>24098.54</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,83 +535,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2060000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>246385.54</t>
+          <t>2319980</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>246383</t>
+          <t>275433.59</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>246383</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2.54</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>29050.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,83 +562,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2319980</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>275433.59</t>
+          <t>2319980</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>246383</t>
+          <t>275433.59</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>275431</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>29050.59</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,83 +604,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2319980</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>275433.59</t>
+          <t>2569980</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>275431</t>
+          <t>305373.71</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>275431</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2.59</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>29942.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,83 +631,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2569980</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>305373.71</t>
+          <t>2569980</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>275431</t>
+          <t>305373.71</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>305371</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>29942.71</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,83 +673,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2569980</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>305373.71</t>
+          <t>2690969</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>305371</t>
+          <t>318816.93</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>305371</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2.71</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13445.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,83 +700,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2690969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>318816.93</t>
+          <t>2690969</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>305371</t>
+          <t>318816.93</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>305459</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>13445.93</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>13357.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -607,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -727,83 +742,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2690969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>318816.93</t>
+          <t>3060969</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>305459</t>
+          <t>363395.24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>305459</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>13357.93</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>57936.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,83 +769,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3060969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>363395.24</t>
+          <t>3060969</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>305459</t>
+          <t>363395.24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>306459</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>57936.24</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>56936.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,83 +796,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3060969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>363395.24</t>
+          <t>3060969</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>306459</t>
+          <t>363395.24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>363392</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>56936.24</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,83 +838,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3060969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>363395.24</t>
+          <t>3160969</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>363392</t>
+          <t>375371.29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>363392</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>3.24</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>11979.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,83 +865,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3160969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>375371.29</t>
+          <t>3160969</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>363392</t>
+          <t>375371.29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>375368</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>11979.29</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -664,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -718,7 +733,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -892,83 +907,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3160969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>375371.29</t>
+          <t>3380969</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>375368</t>
+          <t>401561.77</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>375368</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3.29</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>26193.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,83 +934,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>3380969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>401561.77</t>
+          <t>3380969</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>375368</t>
+          <t>401561.77</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>401558</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>26193.77</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +721,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -787,7 +802,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -799,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -826,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +856,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -961,83 +976,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3380969</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>401561.77</t>
+          <t>3413666</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>401558</t>
+          <t>405320.04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>401558</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3.77</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3762.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -706,12 +706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -733,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1003,83 +1003,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3413666</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>405320.04</t>
+          <t>3413666</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>401558</t>
+          <t>405320.04</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>405316</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3762.04</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,166 +579,181 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +790,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -802,7 +817,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -814,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -856,7 +871,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -868,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -895,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +925,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -922,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -949,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -976,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1003,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1030,83 +1045,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3413666</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>405320.04</t>
+          <t>3465662</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>405316</t>
+          <t>411296.59</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>405316</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4.04</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5980.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -748,12 +748,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1045,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,83 +1072,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3465662</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>411296.59</t>
+          <t>3465662</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>405316</t>
+          <t>411296.59</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>411292</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>5980.59</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,166 +621,181 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -790,7 +805,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -802,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -844,7 +859,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -856,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -871,7 +886,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -883,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -925,7 +940,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -937,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -979,7 +994,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -991,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1018,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1045,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1099,83 +1114,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3465662</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>411296.59</t>
+          <t>3468006.6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>411292</t>
+          <t>413641.19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>411292</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>4.59</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2349.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,7 +90,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -832,7 +847,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -886,7 +901,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -913,7 +928,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -925,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -967,7 +982,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -979,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1006,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1021,7 +1036,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1033,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1060,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1087,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1114,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1141,83 +1156,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>3468006.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>413641.19</t>
+          <t>3488404.6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>411292</t>
+          <t>415985.79</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>411292</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2349.19</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4693.79</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -874,7 +889,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -928,7 +943,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -940,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -955,7 +970,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -967,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1009,7 +1024,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1021,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1048,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1063,7 +1078,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1075,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1102,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1129,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1156,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,83 +1198,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>3488404.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>415985.79</t>
+          <t>3520501.6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>411292</t>
+          <t>419675.1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>411292</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>4693.79</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>8383.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -874,12 +874,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1063,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1117,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1144,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1198,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,83 +1225,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3520501.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>419675.1</t>
+          <t>3520501.6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>411292</t>
+          <t>419675.1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>417325</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>8383.1</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2350.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,7 +174,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,166 +747,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -916,7 +931,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -928,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -943,7 +958,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -955,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -997,7 +1012,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1009,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1024,7 +1039,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1036,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1078,7 +1093,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1090,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1132,7 +1147,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1144,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1198,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1252,83 +1267,110 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3520501.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>419675.1</t>
+          <t>3580501.6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>417325</t>
+          <t>427082.51</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>417325</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2350.1</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>9757.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -916,12 +916,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -970,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1024,12 +1024,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1105,12 +1105,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1132,12 +1132,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1213,12 +1213,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1267,12 +1267,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1294,83 +1294,110 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>3580501.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>427082.51</t>
+          <t>3580501.6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>417325</t>
+          <t>427082.51</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>424732</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>9757.51</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2350.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -958,7 +973,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -970,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -985,7 +1000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -997,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1012,7 +1027,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1024,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1051,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1066,7 +1081,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1078,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1093,7 +1108,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1105,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1132,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1147,7 +1162,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1159,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1201,7 +1216,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1213,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1240,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1267,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1294,12 +1309,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1321,83 +1336,110 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3580501.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>427082.51</t>
+          <t>3620501.6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>424732</t>
+          <t>432020.78</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>424732</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2350.51</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7288.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -958,12 +958,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -985,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1012,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1120,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1255,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1282,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1336,12 +1336,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1363,83 +1363,110 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3620501.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>432020.78</t>
+          <t>3620501.6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>424732</t>
+          <t>432020.78</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>429670</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>7288.78</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2350.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,7 +258,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1000,7 +1015,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1012,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1027,7 +1042,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1039,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1054,7 +1069,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1066,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1081,7 +1096,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1093,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1120,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,7 +1150,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1147,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1162,7 +1177,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1174,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1216,7 +1231,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1228,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1255,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1270,7 +1285,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1282,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1309,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1336,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1363,12 +1378,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1390,83 +1405,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3620501.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>432020.78</t>
+          <t>3703945.1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>429670</t>
+          <t>442196.82</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>429670</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2350.78</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12526.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1000,12 +1000,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1054,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1081,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1189,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1270,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1324,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1351,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1432,83 +1432,110 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3703945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>442196.82</t>
+          <t>3703945.1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>429670</t>
+          <t>442196.82</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>439846</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>12526.82</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2350.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,7 +300,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1069,7 +1084,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1081,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1096,7 +1111,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1108,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1123,7 +1138,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1135,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1150,7 +1165,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1162,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1189,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1204,7 +1219,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1216,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1231,7 +1246,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1243,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1270,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1285,7 +1300,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1297,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1324,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1339,7 +1354,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1351,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1378,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1432,12 +1447,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1459,83 +1474,110 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3703945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>442196.82</t>
+          <t>3803945.1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>439846</t>
+          <t>454542.49</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>439846</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2350.82</t>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>14696.49</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1042,12 +1042,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1069,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1258,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1285,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1420,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1501,83 +1501,110 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>3803945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>454542.49</t>
+          <t>3803945.1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>439846</t>
+          <t>454542.49</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>452191</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>14696.49</t>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2351.49</t>
         </is>
       </c>
     </row>
